--- a/assets/docs/lop5/Khoa hoc - Lop 5.xlsx
+++ b/assets/docs/lop5/Khoa hoc - Lop 5.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -884,7 +884,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: VI KHUẨN</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
